--- a/plantilla_peso_derivados.xlsx
+++ b/plantilla_peso_derivados.xlsx
@@ -3,15 +3,23 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94670F4F-2E8E-F646-88BA-19E5328CF01A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Milton Moreno\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DA1E879-C327-0144-9658-9989AD735275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D32F1295-1FAE-453D-8020-9D2C81657810}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -23,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
   <si>
     <t>DIVISIÓN SAN BENITO NICARAGUA</t>
   </si>
@@ -45,7 +56,23 @@
     <t>Versión: Cuarta</t>
   </si>
   <si>
-    <t>Código: SB-ACF-071</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Código:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> SB-ACF-071</t>
+    </r>
   </si>
   <si>
     <t>MONITOREO DE PESO DE PRODUCTOS DERIVADOS</t>
@@ -76,6 +103,12 @@
   </si>
   <si>
     <t>Bocas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>.</t>
   </si>
   <si>
     <t>PRODUCTO(s) y presentacion</t>
@@ -333,7 +366,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -342,6 +375,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -366,6 +410,49 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -451,6 +538,32 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -536,6 +649,47 @@
         <color indexed="64"/>
       </top>
       <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -608,10 +762,32 @@
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -625,204 +801,47 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -833,27 +852,27 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -863,142 +882,303 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{C3DC54C3-E6F8-42D4-B99D-5EC8A49BDF7F}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1034,7 +1214,7 @@
         <xdr:cNvPr id="2" name="Imagen 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80166854-BB29-486F-A6B4-DD2D2D359AB1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1056,9 +1236,6 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1382,267 +1559,267 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC8A75E5-4ECD-4B1C-A20B-A00D7C4ED9D3}">
   <dimension ref="A1:AE52"/>
   <sheetFormatPr defaultColWidth="10.76171875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A1" s="55"/>
-      <c r="B1" s="56"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="88" t="s">
+      <c r="A1" s="104"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="78"/>
-      <c r="Y1" s="77" t="s">
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="111"/>
+      <c r="H1" s="111"/>
+      <c r="I1" s="111"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
+      <c r="V1" s="111"/>
+      <c r="W1" s="111"/>
+      <c r="X1" s="112"/>
+      <c r="Y1" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="Z1" s="56"/>
-      <c r="AA1" s="56"/>
-      <c r="AB1" s="56"/>
-      <c r="AC1" s="56"/>
-      <c r="AD1" s="56"/>
-      <c r="AE1" s="78"/>
+      <c r="Z1" s="117"/>
+      <c r="AA1" s="117"/>
+      <c r="AB1" s="117"/>
+      <c r="AC1" s="117"/>
+      <c r="AD1" s="117"/>
+      <c r="AE1" s="118"/>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A2" s="40"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="41"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="42"/>
-      <c r="Y2" s="40"/>
-      <c r="Z2" s="41"/>
-      <c r="AA2" s="41"/>
-      <c r="AB2" s="41"/>
-      <c r="AC2" s="41"/>
-      <c r="AD2" s="41"/>
-      <c r="AE2" s="42"/>
+      <c r="A2" s="107"/>
+      <c r="B2" s="108"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
+      <c r="O2" s="114"/>
+      <c r="P2" s="114"/>
+      <c r="Q2" s="114"/>
+      <c r="R2" s="114"/>
+      <c r="S2" s="114"/>
+      <c r="T2" s="114"/>
+      <c r="U2" s="114"/>
+      <c r="V2" s="114"/>
+      <c r="W2" s="114"/>
+      <c r="X2" s="115"/>
+      <c r="Y2" s="119"/>
+      <c r="Z2" s="120"/>
+      <c r="AA2" s="120"/>
+      <c r="AB2" s="120"/>
+      <c r="AC2" s="120"/>
+      <c r="AD2" s="120"/>
+      <c r="AE2" s="121"/>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A3" s="90" t="s">
+      <c r="A3" s="122" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="84" t="s">
+      <c r="B3" s="123"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
-      <c r="N3" s="65"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="65"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="65"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="65"/>
-      <c r="U3" s="65"/>
-      <c r="V3" s="65"/>
-      <c r="W3" s="65"/>
-      <c r="X3" s="65"/>
-      <c r="Y3" s="97" t="s">
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="129"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
+      <c r="N3" s="129"/>
+      <c r="O3" s="129"/>
+      <c r="P3" s="129"/>
+      <c r="Q3" s="129"/>
+      <c r="R3" s="129"/>
+      <c r="S3" s="129"/>
+      <c r="T3" s="129"/>
+      <c r="U3" s="129"/>
+      <c r="V3" s="129"/>
+      <c r="W3" s="129"/>
+      <c r="X3" s="129"/>
+      <c r="Y3" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="Z3" s="38"/>
-      <c r="AA3" s="38"/>
-      <c r="AB3" s="38"/>
-      <c r="AC3" s="38"/>
-      <c r="AD3" s="38"/>
-      <c r="AE3" s="39"/>
+      <c r="Z3" s="131"/>
+      <c r="AA3" s="131"/>
+      <c r="AB3" s="131"/>
+      <c r="AC3" s="131"/>
+      <c r="AD3" s="131"/>
+      <c r="AE3" s="132"/>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A4" s="40"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="65"/>
-      <c r="Y4" s="40"/>
-      <c r="Z4" s="41"/>
-      <c r="AA4" s="41"/>
-      <c r="AB4" s="41"/>
-      <c r="AC4" s="41"/>
-      <c r="AD4" s="41"/>
-      <c r="AE4" s="42"/>
+      <c r="A4" s="125"/>
+      <c r="B4" s="126"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="128"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="129"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="129"/>
+      <c r="K4" s="129"/>
+      <c r="L4" s="129"/>
+      <c r="M4" s="129"/>
+      <c r="N4" s="129"/>
+      <c r="O4" s="129"/>
+      <c r="P4" s="129"/>
+      <c r="Q4" s="129"/>
+      <c r="R4" s="129"/>
+      <c r="S4" s="129"/>
+      <c r="T4" s="129"/>
+      <c r="U4" s="129"/>
+      <c r="V4" s="129"/>
+      <c r="W4" s="129"/>
+      <c r="X4" s="129"/>
+      <c r="Y4" s="130"/>
+      <c r="Z4" s="131"/>
+      <c r="AA4" s="131"/>
+      <c r="AB4" s="131"/>
+      <c r="AC4" s="131"/>
+      <c r="AD4" s="131"/>
+      <c r="AE4" s="132"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="91"/>
-      <c r="D5" s="45" t="s">
+      <c r="B5" s="81"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
-      <c r="T5" s="38"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="39"/>
-      <c r="Y5" s="37" t="s">
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
+      <c r="I5" s="87"/>
+      <c r="J5" s="87"/>
+      <c r="K5" s="87"/>
+      <c r="L5" s="87"/>
+      <c r="M5" s="87"/>
+      <c r="N5" s="87"/>
+      <c r="O5" s="87"/>
+      <c r="P5" s="87"/>
+      <c r="Q5" s="87"/>
+      <c r="R5" s="87"/>
+      <c r="S5" s="87"/>
+      <c r="T5" s="87"/>
+      <c r="U5" s="87"/>
+      <c r="V5" s="87"/>
+      <c r="W5" s="87"/>
+      <c r="X5" s="88"/>
+      <c r="Y5" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="Z5" s="38"/>
-      <c r="AA5" s="38"/>
-      <c r="AB5" s="38"/>
-      <c r="AC5" s="38"/>
-      <c r="AD5" s="38"/>
-      <c r="AE5" s="39"/>
-    </row>
-    <row r="6" spans="1:31" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="94"/>
-      <c r="B6" s="95"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="41"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="41"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="41"/>
-      <c r="V6" s="41"/>
-      <c r="W6" s="41"/>
-      <c r="X6" s="42"/>
-      <c r="Y6" s="40"/>
-      <c r="Z6" s="41"/>
-      <c r="AA6" s="41"/>
-      <c r="AB6" s="41"/>
-      <c r="AC6" s="41"/>
-      <c r="AD6" s="41"/>
-      <c r="AE6" s="42"/>
+      <c r="Z5" s="93"/>
+      <c r="AA5" s="93"/>
+      <c r="AB5" s="93"/>
+      <c r="AC5" s="93"/>
+      <c r="AD5" s="93"/>
+      <c r="AE5" s="94"/>
+    </row>
+    <row r="6" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="83"/>
+      <c r="B6" s="84"/>
+      <c r="C6" s="85"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="90"/>
+      <c r="K6" s="90"/>
+      <c r="L6" s="90"/>
+      <c r="M6" s="90"/>
+      <c r="N6" s="90"/>
+      <c r="O6" s="90"/>
+      <c r="P6" s="90"/>
+      <c r="Q6" s="90"/>
+      <c r="R6" s="90"/>
+      <c r="S6" s="90"/>
+      <c r="T6" s="90"/>
+      <c r="U6" s="90"/>
+      <c r="V6" s="90"/>
+      <c r="W6" s="90"/>
+      <c r="X6" s="91"/>
+      <c r="Y6" s="95"/>
+      <c r="Z6" s="96"/>
+      <c r="AA6" s="96"/>
+      <c r="AB6" s="96"/>
+      <c r="AC6" s="96"/>
+      <c r="AD6" s="96"/>
+      <c r="AE6" s="97"/>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="U7" s="80" t="s">
+      <c r="U7" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="V7" s="69"/>
-      <c r="W7" s="69"/>
-      <c r="X7" s="69"/>
-      <c r="Y7" s="69"/>
-      <c r="Z7" s="69"/>
-      <c r="AA7" s="69"/>
-      <c r="AB7" s="69"/>
-      <c r="AC7" s="69"/>
-      <c r="AD7" s="69"/>
-      <c r="AE7" s="81"/>
+      <c r="V7" s="99"/>
+      <c r="W7" s="99"/>
+      <c r="X7" s="99"/>
+      <c r="Y7" s="99"/>
+      <c r="Z7" s="99"/>
+      <c r="AA7" s="99"/>
+      <c r="AB7" s="99"/>
+      <c r="AC7" s="99"/>
+      <c r="AD7" s="99"/>
+      <c r="AE7" s="100"/>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="92"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="64" t="s">
+      <c r="B8" s="101"/>
+      <c r="C8" s="101"/>
+      <c r="D8" s="101"/>
+      <c r="E8" s="101"/>
+      <c r="F8" s="102" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="65"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="64" t="s">
+      <c r="G8" s="102"/>
+      <c r="H8" s="103"/>
+      <c r="I8" s="103"/>
+      <c r="J8" s="103"/>
+      <c r="K8" s="103"/>
+      <c r="L8" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="M8" s="65"/>
-      <c r="N8" s="72"/>
-      <c r="O8" s="53"/>
-      <c r="P8" s="53"/>
-      <c r="Q8" s="53"/>
-      <c r="R8" s="64" t="s">
+      <c r="M8" s="102"/>
+      <c r="N8" s="103"/>
+      <c r="O8" s="103"/>
+      <c r="P8" s="103"/>
+      <c r="Q8" s="103"/>
+      <c r="R8" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="S8" s="65"/>
+      <c r="S8" s="102"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
       <c r="V8" s="2"/>
@@ -1656,110 +1833,110 @@
       <c r="AD8" s="3"/>
       <c r="AE8" s="3"/>
     </row>
-    <row r="9" spans="1:31" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" ht="21" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="73"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="47"/>
-      <c r="K9" s="47"/>
-      <c r="L9" s="47"/>
-      <c r="M9" s="47"/>
-      <c r="N9" s="47"/>
-      <c r="O9" s="47"/>
-      <c r="P9" s="47"/>
-      <c r="Q9" s="47"/>
-      <c r="R9" s="47"/>
-      <c r="S9" s="47"/>
-      <c r="T9" s="47"/>
-      <c r="U9" s="47"/>
-      <c r="V9" s="47"/>
-      <c r="W9" s="47"/>
-      <c r="X9" s="47"/>
-      <c r="Y9" s="47"/>
-      <c r="Z9" s="47"/>
-      <c r="AA9" s="47"/>
-      <c r="AB9" s="47"/>
-      <c r="AC9" s="47"/>
-      <c r="AD9" s="47"/>
-      <c r="AE9" s="48"/>
+      <c r="B9" s="75"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="76"/>
+      <c r="K9" s="76"/>
+      <c r="L9" s="76"/>
+      <c r="M9" s="76"/>
+      <c r="N9" s="76"/>
+      <c r="O9" s="76"/>
+      <c r="P9" s="76"/>
+      <c r="Q9" s="76"/>
+      <c r="R9" s="76"/>
+      <c r="S9" s="76"/>
+      <c r="T9" s="76"/>
+      <c r="U9" s="76"/>
+      <c r="V9" s="76"/>
+      <c r="W9" s="76"/>
+      <c r="X9" s="76"/>
+      <c r="Y9" s="76"/>
+      <c r="Z9" s="76"/>
+      <c r="AA9" s="76"/>
+      <c r="AB9" s="76"/>
+      <c r="AC9" s="76"/>
+      <c r="AD9" s="76"/>
+      <c r="AE9" s="77"/>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="89"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="35"/>
-      <c r="V10" s="35"/>
-      <c r="W10" s="35"/>
-      <c r="X10" s="35"/>
-      <c r="Y10" s="35"/>
-      <c r="Z10" s="35"/>
-      <c r="AA10" s="35"/>
-      <c r="AB10" s="35"/>
-      <c r="AC10" s="35"/>
-      <c r="AD10" s="35"/>
-      <c r="AE10" s="35"/>
+      <c r="B10" s="78"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="61"/>
+      <c r="L10" s="61"/>
+      <c r="M10" s="61"/>
+      <c r="N10" s="61"/>
+      <c r="O10" s="61"/>
+      <c r="P10" s="61"/>
+      <c r="Q10" s="61"/>
+      <c r="R10" s="61"/>
+      <c r="S10" s="61"/>
+      <c r="T10" s="61"/>
+      <c r="U10" s="61"/>
+      <c r="V10" s="61"/>
+      <c r="W10" s="61"/>
+      <c r="X10" s="61"/>
+      <c r="Y10" s="61"/>
+      <c r="Z10" s="61"/>
+      <c r="AA10" s="61"/>
+      <c r="AB10" s="61"/>
+      <c r="AC10" s="61"/>
+      <c r="AD10" s="73"/>
+      <c r="AE10" s="61"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
-      <c r="S11" s="36"/>
-      <c r="T11" s="36"/>
-      <c r="U11" s="36"/>
-      <c r="V11" s="36"/>
-      <c r="W11" s="36"/>
-      <c r="X11" s="36"/>
-      <c r="Y11" s="36"/>
-      <c r="Z11" s="36"/>
-      <c r="AA11" s="36"/>
-      <c r="AB11" s="36"/>
-      <c r="AC11" s="36"/>
-      <c r="AD11" s="36"/>
-      <c r="AE11" s="36"/>
+      <c r="B11" s="79"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="62"/>
+      <c r="K11" s="62"/>
+      <c r="L11" s="62"/>
+      <c r="M11" s="62"/>
+      <c r="N11" s="62"/>
+      <c r="O11" s="62"/>
+      <c r="P11" s="62"/>
+      <c r="Q11" s="62"/>
+      <c r="R11" s="62"/>
+      <c r="S11" s="62"/>
+      <c r="T11" s="62"/>
+      <c r="U11" s="62"/>
+      <c r="V11" s="62"/>
+      <c r="W11" s="62"/>
+      <c r="X11" s="62"/>
+      <c r="Y11" s="62"/>
+      <c r="Z11" s="62"/>
+      <c r="AA11" s="62"/>
+      <c r="AB11" s="62"/>
+      <c r="AC11" s="62"/>
+      <c r="AD11" s="61"/>
+      <c r="AE11" s="62"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A12" s="7"/>
@@ -1870,7 +2047,9 @@
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
+      <c r="J15" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
@@ -1969,7 +2148,9 @@
       <c r="G18" s="14"/>
       <c r="H18" s="14"/>
       <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
+      <c r="J18" s="14" t="s">
+        <v>17</v>
+      </c>
       <c r="K18" s="14"/>
       <c r="L18" s="14"/>
       <c r="M18" s="14"/>
@@ -2092,142 +2273,142 @@
       <c r="AE21" s="10"/>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A22" s="71"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="65"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="65"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="65"/>
-      <c r="H22" s="65"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="65"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="65"/>
-      <c r="M22" s="65"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="65"/>
-      <c r="P22" s="65"/>
-      <c r="Q22" s="65"/>
-      <c r="R22" s="65"/>
-      <c r="S22" s="65"/>
-      <c r="T22" s="65"/>
-      <c r="U22" s="65"/>
-      <c r="V22" s="65"/>
-      <c r="W22" s="65"/>
-      <c r="X22" s="65"/>
-      <c r="Y22" s="65"/>
-      <c r="Z22" s="65"/>
-      <c r="AA22" s="65"/>
-      <c r="AB22" s="65"/>
-      <c r="AC22" s="65"/>
-      <c r="AD22" s="65"/>
-      <c r="AE22" s="65"/>
-    </row>
-    <row r="23" spans="1:31" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="74"/>
+      <c r="B22" s="74"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="74"/>
+      <c r="J22" s="74"/>
+      <c r="K22" s="74"/>
+      <c r="L22" s="74"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="74"/>
+      <c r="P22" s="74"/>
+      <c r="Q22" s="74"/>
+      <c r="R22" s="74"/>
+      <c r="S22" s="74"/>
+      <c r="T22" s="74"/>
+      <c r="U22" s="74"/>
+      <c r="V22" s="74"/>
+      <c r="W22" s="74"/>
+      <c r="X22" s="74"/>
+      <c r="Y22" s="74"/>
+      <c r="Z22" s="74"/>
+      <c r="AA22" s="74"/>
+      <c r="AB22" s="74"/>
+      <c r="AC22" s="74"/>
+      <c r="AD22" s="74"/>
+      <c r="AE22" s="74"/>
+    </row>
+    <row r="23" spans="1:31" ht="21" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" s="73"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
-      <c r="M23" s="47"/>
-      <c r="N23" s="47"/>
-      <c r="O23" s="47"/>
-      <c r="P23" s="47"/>
-      <c r="Q23" s="47"/>
-      <c r="R23" s="47"/>
-      <c r="S23" s="47"/>
-      <c r="T23" s="47"/>
-      <c r="U23" s="47"/>
-      <c r="V23" s="47"/>
-      <c r="W23" s="47"/>
-      <c r="X23" s="47"/>
-      <c r="Y23" s="47"/>
-      <c r="Z23" s="47"/>
-      <c r="AA23" s="47"/>
-      <c r="AB23" s="47"/>
-      <c r="AC23" s="47"/>
-      <c r="AD23" s="47"/>
-      <c r="AE23" s="48"/>
+        <v>18</v>
+      </c>
+      <c r="B23" s="75"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76"/>
+      <c r="J23" s="76"/>
+      <c r="K23" s="76"/>
+      <c r="L23" s="76"/>
+      <c r="M23" s="76"/>
+      <c r="N23" s="76"/>
+      <c r="O23" s="76"/>
+      <c r="P23" s="76"/>
+      <c r="Q23" s="76"/>
+      <c r="R23" s="76"/>
+      <c r="S23" s="76"/>
+      <c r="T23" s="76"/>
+      <c r="U23" s="76"/>
+      <c r="V23" s="76"/>
+      <c r="W23" s="76"/>
+      <c r="X23" s="76"/>
+      <c r="Y23" s="76"/>
+      <c r="Z23" s="76"/>
+      <c r="AA23" s="76"/>
+      <c r="AB23" s="76"/>
+      <c r="AC23" s="76"/>
+      <c r="AD23" s="76"/>
+      <c r="AE23" s="77"/>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="89"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="35"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="35"/>
-      <c r="Q24" s="35"/>
-      <c r="R24" s="35"/>
-      <c r="S24" s="35"/>
-      <c r="T24" s="35"/>
-      <c r="U24" s="35"/>
-      <c r="V24" s="35"/>
-      <c r="W24" s="35"/>
-      <c r="X24" s="35"/>
-      <c r="Y24" s="35"/>
-      <c r="Z24" s="35"/>
-      <c r="AA24" s="35"/>
-      <c r="AB24" s="35"/>
-      <c r="AC24" s="35"/>
-      <c r="AD24" s="35"/>
-      <c r="AE24" s="35"/>
+      <c r="B24" s="78"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="61"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="61"/>
+      <c r="K24" s="61"/>
+      <c r="L24" s="61"/>
+      <c r="M24" s="61"/>
+      <c r="N24" s="61"/>
+      <c r="O24" s="61"/>
+      <c r="P24" s="61"/>
+      <c r="Q24" s="61"/>
+      <c r="R24" s="61"/>
+      <c r="S24" s="61"/>
+      <c r="T24" s="61"/>
+      <c r="U24" s="61"/>
+      <c r="V24" s="61"/>
+      <c r="W24" s="61"/>
+      <c r="X24" s="61"/>
+      <c r="Y24" s="61"/>
+      <c r="Z24" s="61"/>
+      <c r="AA24" s="61"/>
+      <c r="AB24" s="61"/>
+      <c r="AC24" s="61"/>
+      <c r="AD24" s="73"/>
+      <c r="AE24" s="61"/>
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="36"/>
-      <c r="K25" s="36"/>
-      <c r="L25" s="36"/>
-      <c r="M25" s="36"/>
-      <c r="N25" s="36"/>
-      <c r="O25" s="36"/>
-      <c r="P25" s="36"/>
-      <c r="Q25" s="36"/>
-      <c r="R25" s="36"/>
-      <c r="S25" s="36"/>
-      <c r="T25" s="36"/>
-      <c r="U25" s="36"/>
-      <c r="V25" s="36"/>
-      <c r="W25" s="36"/>
-      <c r="X25" s="36"/>
-      <c r="Y25" s="36"/>
-      <c r="Z25" s="36"/>
-      <c r="AA25" s="36"/>
-      <c r="AB25" s="36"/>
-      <c r="AC25" s="36"/>
-      <c r="AD25" s="36"/>
-      <c r="AE25" s="36"/>
+      <c r="B25" s="79"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="62"/>
+      <c r="I25" s="62"/>
+      <c r="J25" s="62"/>
+      <c r="K25" s="62"/>
+      <c r="L25" s="62"/>
+      <c r="M25" s="62"/>
+      <c r="N25" s="62"/>
+      <c r="O25" s="62"/>
+      <c r="P25" s="62"/>
+      <c r="Q25" s="62"/>
+      <c r="R25" s="62"/>
+      <c r="S25" s="62"/>
+      <c r="T25" s="62"/>
+      <c r="U25" s="62"/>
+      <c r="V25" s="62"/>
+      <c r="W25" s="62"/>
+      <c r="X25" s="62"/>
+      <c r="Y25" s="62"/>
+      <c r="Z25" s="62"/>
+      <c r="AA25" s="62"/>
+      <c r="AB25" s="62"/>
+      <c r="AC25" s="62"/>
+      <c r="AD25" s="61"/>
+      <c r="AE25" s="62"/>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A26" s="7"/>
@@ -2526,7 +2707,7 @@
       <c r="AD34" s="10"/>
       <c r="AE34" s="10"/>
     </row>
-    <row r="35" spans="1:31" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
@@ -2560,191 +2741,191 @@
       <c r="AE35" s="15"/>
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A36" s="74" t="s">
-        <v>17</v>
-      </c>
-      <c r="B36" s="69"/>
-      <c r="C36" s="69"/>
-      <c r="D36" s="69"/>
-      <c r="E36" s="69"/>
-      <c r="F36" s="69"/>
-      <c r="G36" s="70"/>
+      <c r="A36" s="63" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36" s="64"/>
+      <c r="C36" s="64"/>
+      <c r="D36" s="64"/>
+      <c r="E36" s="64"/>
+      <c r="F36" s="64"/>
+      <c r="G36" s="65"/>
       <c r="H36" s="17"/>
       <c r="I36" s="18"/>
-      <c r="J36" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="K36" s="69"/>
-      <c r="L36" s="69"/>
-      <c r="M36" s="69"/>
-      <c r="N36" s="69"/>
-      <c r="O36" s="69"/>
-      <c r="P36" s="69"/>
-      <c r="Q36" s="69"/>
-      <c r="R36" s="70"/>
+      <c r="J36" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="K36" s="67"/>
+      <c r="L36" s="67"/>
+      <c r="M36" s="67"/>
+      <c r="N36" s="67"/>
+      <c r="O36" s="67"/>
+      <c r="P36" s="67"/>
+      <c r="Q36" s="67"/>
+      <c r="R36" s="68"/>
       <c r="S36" s="17"/>
-      <c r="T36" s="83" t="s">
-        <v>19</v>
-      </c>
-      <c r="U36" s="69"/>
-      <c r="V36" s="69"/>
-      <c r="W36" s="69"/>
-      <c r="X36" s="69"/>
-      <c r="Y36" s="69"/>
-      <c r="Z36" s="69"/>
-      <c r="AA36" s="69"/>
-      <c r="AB36" s="69"/>
-      <c r="AC36" s="69"/>
-      <c r="AD36" s="69"/>
-      <c r="AE36" s="70"/>
+      <c r="T36" s="69" t="s">
+        <v>21</v>
+      </c>
+      <c r="U36" s="70"/>
+      <c r="V36" s="70"/>
+      <c r="W36" s="70"/>
+      <c r="X36" s="70"/>
+      <c r="Y36" s="70"/>
+      <c r="Z36" s="70"/>
+      <c r="AA36" s="70"/>
+      <c r="AB36" s="70"/>
+      <c r="AC36" s="70"/>
+      <c r="AD36" s="70"/>
+      <c r="AE36" s="71"/>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A37" s="61" t="s">
-        <v>20</v>
-      </c>
-      <c r="B37" s="63"/>
-      <c r="C37" s="75" t="s">
-        <v>21</v>
-      </c>
-      <c r="D37" s="47"/>
-      <c r="E37" s="47"/>
-      <c r="F37" s="47"/>
-      <c r="G37" s="48"/>
+      <c r="A37" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="51"/>
+      <c r="C37" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" s="51"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="52"/>
       <c r="H37" s="19"/>
       <c r="I37" s="20"/>
-      <c r="J37" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="K37" s="62"/>
-      <c r="L37" s="62"/>
-      <c r="M37" s="62"/>
-      <c r="N37" s="63"/>
-      <c r="O37" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="P37" s="47"/>
-      <c r="Q37" s="47"/>
-      <c r="R37" s="48"/>
+      <c r="J37" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="K37" s="58"/>
+      <c r="L37" s="58"/>
+      <c r="M37" s="58"/>
+      <c r="N37" s="58"/>
+      <c r="O37" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="P37" s="58"/>
+      <c r="Q37" s="58"/>
+      <c r="R37" s="60"/>
       <c r="S37" s="19"/>
-      <c r="T37" s="61" t="s">
-        <v>24</v>
-      </c>
-      <c r="U37" s="62"/>
-      <c r="V37" s="62"/>
-      <c r="W37" s="62"/>
-      <c r="X37" s="62"/>
-      <c r="Y37" s="63"/>
-      <c r="Z37" s="66" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA37" s="47"/>
-      <c r="AB37" s="47"/>
-      <c r="AC37" s="47"/>
-      <c r="AD37" s="47"/>
-      <c r="AE37" s="48"/>
+      <c r="T37" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="U37" s="51"/>
+      <c r="V37" s="51"/>
+      <c r="W37" s="51"/>
+      <c r="X37" s="51"/>
+      <c r="Y37" s="51"/>
+      <c r="Z37" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA37" s="55"/>
+      <c r="AB37" s="55"/>
+      <c r="AC37" s="55"/>
+      <c r="AD37" s="55"/>
+      <c r="AE37" s="56"/>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A38" s="61" t="s">
-        <v>26</v>
-      </c>
-      <c r="B38" s="63"/>
-      <c r="C38" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="D38" s="47"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="48"/>
+      <c r="A38" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" s="51"/>
+      <c r="C38" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="51"/>
+      <c r="G38" s="52"/>
       <c r="H38" s="19"/>
       <c r="I38" s="20"/>
-      <c r="J38" s="67" t="s">
-        <v>28</v>
-      </c>
-      <c r="K38" s="62"/>
-      <c r="L38" s="62"/>
-      <c r="M38" s="62"/>
-      <c r="N38" s="63"/>
-      <c r="O38" s="87" t="s">
-        <v>29</v>
-      </c>
-      <c r="P38" s="47"/>
-      <c r="Q38" s="47"/>
-      <c r="R38" s="48"/>
+      <c r="J38" s="57" t="s">
+        <v>30</v>
+      </c>
+      <c r="K38" s="58"/>
+      <c r="L38" s="58"/>
+      <c r="M38" s="58"/>
+      <c r="N38" s="58"/>
+      <c r="O38" s="59" t="s">
+        <v>31</v>
+      </c>
+      <c r="P38" s="58"/>
+      <c r="Q38" s="58"/>
+      <c r="R38" s="60"/>
       <c r="S38" s="19"/>
-      <c r="T38" s="61" t="s">
-        <v>30</v>
-      </c>
-      <c r="U38" s="62"/>
-      <c r="V38" s="62"/>
-      <c r="W38" s="62"/>
-      <c r="X38" s="62"/>
-      <c r="Y38" s="63"/>
-      <c r="Z38" s="66" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA38" s="47"/>
-      <c r="AB38" s="47"/>
-      <c r="AC38" s="47"/>
-      <c r="AD38" s="47"/>
-      <c r="AE38" s="48"/>
-    </row>
-    <row r="39" spans="1:31" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="61" t="s">
+      <c r="T38" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="63"/>
-      <c r="C39" s="75" t="s">
+      <c r="U38" s="51"/>
+      <c r="V38" s="51"/>
+      <c r="W38" s="51"/>
+      <c r="X38" s="51"/>
+      <c r="Y38" s="51"/>
+      <c r="Z38" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="48"/>
+      <c r="AA38" s="55"/>
+      <c r="AB38" s="55"/>
+      <c r="AC38" s="55"/>
+      <c r="AD38" s="55"/>
+      <c r="AE38" s="56"/>
+    </row>
+    <row r="39" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="51"/>
+      <c r="C39" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D39" s="51"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="51"/>
+      <c r="G39" s="52"/>
       <c r="H39" s="19"/>
       <c r="I39" s="20"/>
-      <c r="J39" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="K39" s="50"/>
-      <c r="L39" s="50"/>
-      <c r="M39" s="50"/>
-      <c r="N39" s="51"/>
-      <c r="O39" s="79" t="s">
+      <c r="J39" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="K39" s="45"/>
+      <c r="L39" s="45"/>
+      <c r="M39" s="45"/>
+      <c r="N39" s="45"/>
+      <c r="O39" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="P39" s="53"/>
+      <c r="Q39" s="53"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="19"/>
+      <c r="T39" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="U39" s="51"/>
+      <c r="V39" s="51"/>
+      <c r="W39" s="51"/>
+      <c r="X39" s="51"/>
+      <c r="Y39" s="51"/>
+      <c r="Z39" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="P39" s="50"/>
-      <c r="Q39" s="50"/>
-      <c r="R39" s="51"/>
-      <c r="S39" s="19"/>
-      <c r="T39" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="U39" s="62"/>
-      <c r="V39" s="62"/>
-      <c r="W39" s="62"/>
-      <c r="X39" s="62"/>
-      <c r="Y39" s="63"/>
-      <c r="Z39" s="66" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA39" s="47"/>
-      <c r="AB39" s="47"/>
-      <c r="AC39" s="47"/>
-      <c r="AD39" s="47"/>
-      <c r="AE39" s="48"/>
-    </row>
-    <row r="40" spans="1:31" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="51"/>
-      <c r="C40" s="59" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" s="50"/>
-      <c r="E40" s="50"/>
-      <c r="F40" s="50"/>
-      <c r="G40" s="51"/>
+      <c r="AA39" s="55"/>
+      <c r="AB39" s="55"/>
+      <c r="AC39" s="55"/>
+      <c r="AD39" s="55"/>
+      <c r="AE39" s="56"/>
+    </row>
+    <row r="40" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="44" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="45"/>
+      <c r="C40" s="45" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" s="45"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="46"/>
       <c r="H40" s="21"/>
       <c r="I40" s="22"/>
       <c r="J40" s="22"/>
@@ -2757,63 +2938,63 @@
       <c r="Q40" s="23"/>
       <c r="R40" s="23"/>
       <c r="S40" s="21"/>
-      <c r="T40" s="49" t="s">
-        <v>39</v>
-      </c>
-      <c r="U40" s="50"/>
-      <c r="V40" s="50"/>
-      <c r="W40" s="50"/>
-      <c r="X40" s="50"/>
-      <c r="Y40" s="51"/>
-      <c r="Z40" s="82" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA40" s="50"/>
-      <c r="AB40" s="50"/>
-      <c r="AC40" s="50"/>
-      <c r="AD40" s="50"/>
-      <c r="AE40" s="51"/>
+      <c r="T40" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="U40" s="45"/>
+      <c r="V40" s="45"/>
+      <c r="W40" s="45"/>
+      <c r="X40" s="45"/>
+      <c r="Y40" s="45"/>
+      <c r="Z40" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA40" s="47"/>
+      <c r="AB40" s="47"/>
+      <c r="AC40" s="47"/>
+      <c r="AD40" s="47"/>
+      <c r="AE40" s="48"/>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A41" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" s="53"/>
-      <c r="D41" s="53"/>
-      <c r="E41" s="54"/>
-      <c r="F41" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="G41" s="53"/>
-      <c r="H41" s="53"/>
-      <c r="I41" s="53"/>
-      <c r="J41" s="53"/>
-      <c r="K41" s="53"/>
-      <c r="L41" s="53"/>
-      <c r="M41" s="53"/>
-      <c r="N41" s="53"/>
-      <c r="O41" s="53"/>
-      <c r="P41" s="53"/>
-      <c r="Q41" s="53"/>
-      <c r="R41" s="53"/>
-      <c r="S41" s="53"/>
-      <c r="T41" s="53"/>
-      <c r="U41" s="53"/>
-      <c r="V41" s="53"/>
-      <c r="W41" s="53"/>
-      <c r="X41" s="53"/>
-      <c r="Y41" s="54"/>
-      <c r="Z41" s="52" t="s">
+      <c r="B41" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="AA41" s="53"/>
-      <c r="AB41" s="53"/>
-      <c r="AC41" s="53"/>
-      <c r="AD41" s="53"/>
-      <c r="AE41" s="54"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="G41" s="49"/>
+      <c r="H41" s="49"/>
+      <c r="I41" s="49"/>
+      <c r="J41" s="49"/>
+      <c r="K41" s="49"/>
+      <c r="L41" s="49"/>
+      <c r="M41" s="49"/>
+      <c r="N41" s="49"/>
+      <c r="O41" s="49"/>
+      <c r="P41" s="49"/>
+      <c r="Q41" s="49"/>
+      <c r="R41" s="49"/>
+      <c r="S41" s="49"/>
+      <c r="T41" s="49"/>
+      <c r="U41" s="49"/>
+      <c r="V41" s="49"/>
+      <c r="W41" s="49"/>
+      <c r="X41" s="49"/>
+      <c r="Y41" s="49"/>
+      <c r="Z41" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA41" s="49"/>
+      <c r="AB41" s="49"/>
+      <c r="AC41" s="49"/>
+      <c r="AD41" s="49"/>
+      <c r="AE41" s="49"/>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A42" s="25"/>
@@ -2821,32 +3002,32 @@
       <c r="C42" s="27"/>
       <c r="D42" s="27"/>
       <c r="E42" s="28"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="53"/>
-      <c r="H42" s="53"/>
-      <c r="I42" s="53"/>
-      <c r="J42" s="53"/>
-      <c r="K42" s="53"/>
-      <c r="L42" s="53"/>
-      <c r="M42" s="53"/>
-      <c r="N42" s="53"/>
-      <c r="O42" s="53"/>
-      <c r="P42" s="53"/>
-      <c r="Q42" s="53"/>
-      <c r="R42" s="53"/>
-      <c r="S42" s="53"/>
-      <c r="T42" s="53"/>
-      <c r="U42" s="53"/>
-      <c r="V42" s="53"/>
-      <c r="W42" s="53"/>
-      <c r="X42" s="53"/>
-      <c r="Y42" s="54"/>
-      <c r="Z42" s="52"/>
-      <c r="AA42" s="53"/>
-      <c r="AB42" s="53"/>
-      <c r="AC42" s="53"/>
-      <c r="AD42" s="53"/>
-      <c r="AE42" s="54"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="39"/>
+      <c r="H42" s="39"/>
+      <c r="I42" s="39"/>
+      <c r="J42" s="39"/>
+      <c r="K42" s="39"/>
+      <c r="L42" s="39"/>
+      <c r="M42" s="39"/>
+      <c r="N42" s="39"/>
+      <c r="O42" s="39"/>
+      <c r="P42" s="39"/>
+      <c r="Q42" s="39"/>
+      <c r="R42" s="39"/>
+      <c r="S42" s="39"/>
+      <c r="T42" s="39"/>
+      <c r="U42" s="39"/>
+      <c r="V42" s="39"/>
+      <c r="W42" s="39"/>
+      <c r="X42" s="39"/>
+      <c r="Y42" s="40"/>
+      <c r="Z42" s="38"/>
+      <c r="AA42" s="39"/>
+      <c r="AB42" s="39"/>
+      <c r="AC42" s="39"/>
+      <c r="AD42" s="39"/>
+      <c r="AE42" s="40"/>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A43" s="25"/>
@@ -2920,32 +3101,32 @@
       <c r="C45" s="27"/>
       <c r="D45" s="27"/>
       <c r="E45" s="28"/>
-      <c r="F45" s="76"/>
-      <c r="G45" s="47"/>
-      <c r="H45" s="47"/>
-      <c r="I45" s="47"/>
-      <c r="J45" s="47"/>
-      <c r="K45" s="47"/>
-      <c r="L45" s="47"/>
-      <c r="M45" s="47"/>
-      <c r="N45" s="47"/>
-      <c r="O45" s="47"/>
-      <c r="P45" s="47"/>
-      <c r="Q45" s="47"/>
-      <c r="R45" s="47"/>
-      <c r="S45" s="47"/>
-      <c r="T45" s="47"/>
-      <c r="U45" s="47"/>
-      <c r="V45" s="47"/>
-      <c r="W45" s="47"/>
-      <c r="X45" s="47"/>
-      <c r="Y45" s="48"/>
-      <c r="Z45" s="76"/>
-      <c r="AA45" s="47"/>
-      <c r="AB45" s="47"/>
-      <c r="AC45" s="47"/>
-      <c r="AD45" s="47"/>
-      <c r="AE45" s="48"/>
+      <c r="F45" s="41"/>
+      <c r="G45" s="42"/>
+      <c r="H45" s="42"/>
+      <c r="I45" s="42"/>
+      <c r="J45" s="42"/>
+      <c r="K45" s="42"/>
+      <c r="L45" s="42"/>
+      <c r="M45" s="42"/>
+      <c r="N45" s="42"/>
+      <c r="O45" s="42"/>
+      <c r="P45" s="42"/>
+      <c r="Q45" s="42"/>
+      <c r="R45" s="42"/>
+      <c r="S45" s="42"/>
+      <c r="T45" s="42"/>
+      <c r="U45" s="42"/>
+      <c r="V45" s="42"/>
+      <c r="W45" s="42"/>
+      <c r="X45" s="42"/>
+      <c r="Y45" s="43"/>
+      <c r="Z45" s="41"/>
+      <c r="AA45" s="42"/>
+      <c r="AB45" s="42"/>
+      <c r="AC45" s="42"/>
+      <c r="AD45" s="42"/>
+      <c r="AE45" s="43"/>
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A46" s="25"/>
@@ -2953,32 +3134,32 @@
       <c r="C46" s="27"/>
       <c r="D46" s="27"/>
       <c r="E46" s="28"/>
-      <c r="F46" s="76"/>
-      <c r="G46" s="47"/>
-      <c r="H46" s="47"/>
-      <c r="I46" s="47"/>
-      <c r="J46" s="47"/>
-      <c r="K46" s="47"/>
-      <c r="L46" s="47"/>
-      <c r="M46" s="47"/>
-      <c r="N46" s="47"/>
-      <c r="O46" s="47"/>
-      <c r="P46" s="47"/>
-      <c r="Q46" s="47"/>
-      <c r="R46" s="47"/>
-      <c r="S46" s="47"/>
-      <c r="T46" s="47"/>
-      <c r="U46" s="47"/>
-      <c r="V46" s="47"/>
-      <c r="W46" s="47"/>
-      <c r="X46" s="47"/>
-      <c r="Y46" s="48"/>
-      <c r="Z46" s="76"/>
-      <c r="AA46" s="47"/>
-      <c r="AB46" s="47"/>
-      <c r="AC46" s="47"/>
-      <c r="AD46" s="47"/>
-      <c r="AE46" s="48"/>
+      <c r="F46" s="41"/>
+      <c r="G46" s="42"/>
+      <c r="H46" s="42"/>
+      <c r="I46" s="42"/>
+      <c r="J46" s="42"/>
+      <c r="K46" s="42"/>
+      <c r="L46" s="42"/>
+      <c r="M46" s="42"/>
+      <c r="N46" s="42"/>
+      <c r="O46" s="42"/>
+      <c r="P46" s="42"/>
+      <c r="Q46" s="42"/>
+      <c r="R46" s="42"/>
+      <c r="S46" s="42"/>
+      <c r="T46" s="42"/>
+      <c r="U46" s="42"/>
+      <c r="V46" s="42"/>
+      <c r="W46" s="42"/>
+      <c r="X46" s="42"/>
+      <c r="Y46" s="43"/>
+      <c r="Z46" s="41"/>
+      <c r="AA46" s="42"/>
+      <c r="AB46" s="42"/>
+      <c r="AC46" s="42"/>
+      <c r="AD46" s="42"/>
+      <c r="AE46" s="43"/>
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A47" s="32"/>
@@ -3014,11 +3195,11 @@
       <c r="AE47" s="3"/>
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A48" s="86" t="s">
-        <v>45</v>
-      </c>
-      <c r="B48" s="44"/>
-      <c r="C48" s="44"/>
+      <c r="A48" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="36"/>
+      <c r="C48" s="36"/>
       <c r="D48" s="32"/>
       <c r="E48" s="32"/>
       <c r="F48" s="32"/>
@@ -3026,15 +3207,15 @@
       <c r="H48" s="32"/>
       <c r="I48" s="32"/>
       <c r="J48" s="32"/>
-      <c r="K48" s="86" t="s">
-        <v>46</v>
-      </c>
-      <c r="L48" s="44"/>
-      <c r="M48" s="44"/>
-      <c r="N48" s="44"/>
-      <c r="O48" s="44"/>
-      <c r="P48" s="44"/>
-      <c r="Q48" s="44"/>
+      <c r="K48" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="L48" s="36"/>
+      <c r="M48" s="36"/>
+      <c r="N48" s="36"/>
+      <c r="O48" s="36"/>
+      <c r="P48" s="36"/>
+      <c r="Q48" s="36"/>
       <c r="R48" s="3"/>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
@@ -3042,14 +3223,14 @@
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
       <c r="X48" s="3"/>
-      <c r="Y48" s="60" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z48" s="44"/>
-      <c r="AA48" s="44"/>
-      <c r="AB48" s="44"/>
-      <c r="AC48" s="44"/>
-      <c r="AD48" s="44"/>
+      <c r="Y48" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z48" s="37"/>
+      <c r="AA48" s="37"/>
+      <c r="AB48" s="37"/>
+      <c r="AC48" s="37"/>
+      <c r="AD48" s="37"/>
       <c r="AE48" s="3"/>
     </row>
     <row r="49" spans="1:31" x14ac:dyDescent="0.2">
@@ -3086,11 +3267,11 @@
       <c r="AE49" s="3"/>
     </row>
     <row r="50" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A50" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="B50" s="44"/>
-      <c r="C50" s="44"/>
+      <c r="A50" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50" s="37"/>
+      <c r="C50" s="37"/>
       <c r="D50" s="34"/>
       <c r="E50" s="34"/>
       <c r="F50" s="34"/>
@@ -3098,163 +3279,163 @@
       <c r="H50" s="34"/>
       <c r="I50" s="34"/>
       <c r="J50" s="34"/>
-      <c r="K50" s="60" t="s">
-        <v>49</v>
-      </c>
-      <c r="L50" s="44"/>
-      <c r="M50" s="44"/>
-      <c r="N50" s="44"/>
-      <c r="O50" s="44"/>
-      <c r="P50" s="44"/>
-      <c r="Q50" s="44"/>
-      <c r="Y50" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z50" s="44"/>
-      <c r="AA50" s="44"/>
-      <c r="AB50" s="44"/>
-      <c r="AC50" s="44"/>
-      <c r="AD50" s="44"/>
+      <c r="K50" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="L50" s="37"/>
+      <c r="M50" s="37"/>
+      <c r="N50" s="37"/>
+      <c r="O50" s="37"/>
+      <c r="P50" s="37"/>
+      <c r="Q50" s="37"/>
+      <c r="Y50" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z50" s="37"/>
+      <c r="AA50" s="37"/>
+      <c r="AB50" s="37"/>
+      <c r="AC50" s="37"/>
+      <c r="AD50" s="37"/>
     </row>
     <row r="52" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="E52" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="F52" s="44"/>
-      <c r="G52" s="44"/>
-      <c r="H52" s="44"/>
-      <c r="I52" s="44"/>
-      <c r="S52" s="43" t="s">
-        <v>52</v>
-      </c>
-      <c r="T52" s="44"/>
-      <c r="U52" s="44"/>
-      <c r="V52" s="44"/>
-      <c r="W52" s="44"/>
+      <c r="E52" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="F52" s="35"/>
+      <c r="G52" s="35"/>
+      <c r="H52" s="35"/>
+      <c r="I52" s="35"/>
+      <c r="S52" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="T52" s="35"/>
+      <c r="U52" s="35"/>
+      <c r="V52" s="35"/>
+      <c r="W52" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="121">
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:X2"/>
+    <mergeCell ref="Y1:AE2"/>
+    <mergeCell ref="A3:C4"/>
+    <mergeCell ref="D3:X4"/>
+    <mergeCell ref="Y3:AE4"/>
+    <mergeCell ref="A5:C6"/>
+    <mergeCell ref="D5:X6"/>
+    <mergeCell ref="Y5:AE6"/>
+    <mergeCell ref="U7:AE7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:Q8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="B9:AE9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="S10:S11"/>
+    <mergeCell ref="T10:T11"/>
+    <mergeCell ref="U10:U11"/>
+    <mergeCell ref="V10:V11"/>
+    <mergeCell ref="K10:K11"/>
+    <mergeCell ref="L10:L11"/>
+    <mergeCell ref="M10:M11"/>
+    <mergeCell ref="N10:N11"/>
+    <mergeCell ref="O10:O11"/>
+    <mergeCell ref="P10:P11"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="I24:I25"/>
+    <mergeCell ref="J24:J25"/>
+    <mergeCell ref="K24:K25"/>
+    <mergeCell ref="L24:L25"/>
+    <mergeCell ref="AC10:AC11"/>
+    <mergeCell ref="AD10:AD11"/>
+    <mergeCell ref="AE10:AE11"/>
+    <mergeCell ref="A22:AE22"/>
+    <mergeCell ref="B23:AE23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="W10:W11"/>
+    <mergeCell ref="X10:X11"/>
+    <mergeCell ref="Y10:Y11"/>
+    <mergeCell ref="Z10:Z11"/>
+    <mergeCell ref="AA10:AA11"/>
+    <mergeCell ref="AB10:AB11"/>
+    <mergeCell ref="Q10:Q11"/>
+    <mergeCell ref="R10:R11"/>
+    <mergeCell ref="U24:U25"/>
+    <mergeCell ref="V24:V25"/>
+    <mergeCell ref="W24:W25"/>
+    <mergeCell ref="X24:X25"/>
+    <mergeCell ref="M24:M25"/>
+    <mergeCell ref="N24:N25"/>
+    <mergeCell ref="O24:O25"/>
+    <mergeCell ref="P24:P25"/>
+    <mergeCell ref="Q24:Q25"/>
+    <mergeCell ref="R24:R25"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="J38:N38"/>
+    <mergeCell ref="O38:R38"/>
+    <mergeCell ref="T38:Y38"/>
+    <mergeCell ref="Z38:AE38"/>
+    <mergeCell ref="AE24:AE25"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="J36:R36"/>
+    <mergeCell ref="T36:AE36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="J37:N37"/>
+    <mergeCell ref="O37:R37"/>
+    <mergeCell ref="T37:Y37"/>
+    <mergeCell ref="Z37:AE37"/>
+    <mergeCell ref="Y24:Y25"/>
+    <mergeCell ref="Z24:Z25"/>
+    <mergeCell ref="AA24:AA25"/>
+    <mergeCell ref="AB24:AB25"/>
+    <mergeCell ref="AC24:AC25"/>
+    <mergeCell ref="AD24:AD25"/>
+    <mergeCell ref="S24:S25"/>
+    <mergeCell ref="T24:T25"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="T40:Y40"/>
+    <mergeCell ref="Z40:AE40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="F41:Y41"/>
+    <mergeCell ref="Z41:AE41"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="J39:N39"/>
+    <mergeCell ref="O39:R39"/>
+    <mergeCell ref="T39:Y39"/>
+    <mergeCell ref="Z39:AE39"/>
+    <mergeCell ref="E52:I52"/>
+    <mergeCell ref="S52:W52"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="K48:Q48"/>
+    <mergeCell ref="Y48:AD48"/>
+    <mergeCell ref="A50:C50"/>
     <mergeCell ref="K50:Q50"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A5:C6"/>
-    <mergeCell ref="Z24:Z25"/>
-    <mergeCell ref="K24:K25"/>
-    <mergeCell ref="T24:T25"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="Y3:AE4"/>
-    <mergeCell ref="W24:W25"/>
-    <mergeCell ref="T10:T11"/>
-    <mergeCell ref="K48:Q48"/>
-    <mergeCell ref="O24:O25"/>
-    <mergeCell ref="R24:R25"/>
-    <mergeCell ref="O38:R38"/>
-    <mergeCell ref="L24:L25"/>
-    <mergeCell ref="B23:AE23"/>
-    <mergeCell ref="D1:X2"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="N10:N11"/>
-    <mergeCell ref="F41:Y41"/>
+    <mergeCell ref="Y50:AD50"/>
+    <mergeCell ref="F42:Y42"/>
+    <mergeCell ref="Z42:AE42"/>
+    <mergeCell ref="F45:Y45"/>
     <mergeCell ref="Z45:AE45"/>
-    <mergeCell ref="A3:C4"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="V10:V11"/>
-    <mergeCell ref="X24:X25"/>
-    <mergeCell ref="Y1:AE2"/>
-    <mergeCell ref="J24:J25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="I24:I25"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="X10:X11"/>
-    <mergeCell ref="F45:Y45"/>
-    <mergeCell ref="Z10:Z11"/>
-    <mergeCell ref="T37:Y37"/>
-    <mergeCell ref="O39:R39"/>
-    <mergeCell ref="U7:AE7"/>
+    <mergeCell ref="F46:Y46"/>
     <mergeCell ref="Z46:AE46"/>
-    <mergeCell ref="Z40:AE40"/>
-    <mergeCell ref="T36:AE36"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="T38:Y38"/>
-    <mergeCell ref="N8:Q8"/>
-    <mergeCell ref="D3:X4"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="S24:S25"/>
-    <mergeCell ref="F42:Y42"/>
-    <mergeCell ref="U24:U25"/>
-    <mergeCell ref="B9:AE9"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="M24:M25"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="F46:Y46"/>
-    <mergeCell ref="U10:U11"/>
-    <mergeCell ref="W10:W11"/>
-    <mergeCell ref="O10:O11"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="P10:P11"/>
-    <mergeCell ref="J37:N37"/>
-    <mergeCell ref="Z41:AE41"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="Q24:Q25"/>
-    <mergeCell ref="AA10:AA11"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="AA24:AA25"/>
-    <mergeCell ref="AC10:AC11"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="AE10:AE11"/>
-    <mergeCell ref="Y48:AD48"/>
-    <mergeCell ref="AE24:AE25"/>
-    <mergeCell ref="N24:N25"/>
-    <mergeCell ref="P24:P25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="T39:Y39"/>
-    <mergeCell ref="AB10:AB11"/>
-    <mergeCell ref="AB24:AB25"/>
-    <mergeCell ref="AD24:AD25"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="R10:R11"/>
-    <mergeCell ref="J39:N39"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="AD10:AD11"/>
-    <mergeCell ref="Z37:AE37"/>
-    <mergeCell ref="J38:N38"/>
-    <mergeCell ref="Y24:Y25"/>
-    <mergeCell ref="Y5:AE6"/>
-    <mergeCell ref="E52:I52"/>
-    <mergeCell ref="D5:X6"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="AC24:AC25"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="S52:W52"/>
-    <mergeCell ref="Y10:Y11"/>
-    <mergeCell ref="O37:R37"/>
-    <mergeCell ref="T40:Y40"/>
-    <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="S10:S11"/>
-    <mergeCell ref="Z42:AE42"/>
-    <mergeCell ref="Y50:AD50"/>
-    <mergeCell ref="J36:R36"/>
-    <mergeCell ref="A22:AE22"/>
-    <mergeCell ref="Z39:AE39"/>
-    <mergeCell ref="M10:M11"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="H8:K8"/>
-    <mergeCell ref="Z38:AE38"/>
-    <mergeCell ref="V24:V25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
